--- a/organizational-architecture/reviews/phase-2-reviews/archive/inventory-analysis-v1.xlsx
+++ b/organizational-architecture/reviews/phase-2-reviews/archive/inventory-analysis-v1.xlsx
@@ -569,7 +569,7 @@
     <t>Escalated Operational Events</t>
   </si>
   <si>
-    <t>Northstar Health Operations</t>
+    <t>Northstar Enterprise</t>
   </si>
   <si>
     <t>Operational Inventory Executive Summary</t>
